--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>预计安装部署、卸载10月15日发布</t>
   </si>
@@ -59,84 +59,94 @@
     <t>接口调整</t>
   </si>
   <si>
+    <t>安装业务</t>
+  </si>
+  <si>
+    <t>scanhost</t>
+  </si>
+  <si>
+    <t>addhost</t>
+  </si>
+  <si>
+    <t>修改为后台并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent重启</t>
+  </si>
+  <si>
+    <t>开始编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卸载机器</t>
+  </si>
+  <si>
+    <t>卸载集群</t>
+  </si>
+  <si>
+    <t>卸载业务</t>
+  </si>
+  <si>
+    <t>开始编码，后台并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面优先显示</t>
+  </si>
+  <si>
+    <t>业务扩容</t>
+  </si>
+  <si>
+    <t>******</t>
+  </si>
+  <si>
+    <t>业务状态</t>
+  </si>
+  <si>
+    <t>启动业务</t>
+  </si>
+  <si>
+    <t>停止业务</t>
+  </si>
+  <si>
+    <t>许建辉、谭钊波、何嘉文、林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与会人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常处理(业务已经存在，版本冲突）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回值定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整为1个机器最耗时1s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>messageReply返回值的模式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安装业务</t>
-  </si>
-  <si>
-    <t>待调试</t>
-  </si>
-  <si>
-    <t>scanhost</t>
-  </si>
-  <si>
-    <t>调整为1个机器最耗时1s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>addhost</t>
-  </si>
-  <si>
-    <t>修改为后台并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>agent重启</t>
-  </si>
-  <si>
-    <t>开始编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卸载机器</t>
-  </si>
-  <si>
-    <t>卸载集群</t>
-  </si>
-  <si>
-    <t>卸载业务</t>
-  </si>
-  <si>
-    <t>开始编码，后台并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>页面优先显示</t>
-  </si>
-  <si>
-    <t>返回值定义</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常处理(业务已经存在，版本冲突）</t>
-  </si>
-  <si>
-    <t>优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务扩容</t>
-  </si>
-  <si>
-    <t>******</t>
-  </si>
-  <si>
-    <t>业务状态</t>
-  </si>
-  <si>
-    <t>启动业务</t>
-  </si>
-  <si>
-    <t>停止业务</t>
-  </si>
-  <si>
-    <t>许建辉、谭钊波、何嘉文、林友滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与会人</t>
+    <t>检测主机信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU占用 内存等</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -609,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -619,10 +629,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27">
@@ -652,140 +662,156 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4" ht="27">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="A17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="7" t="s">
-        <v>25</v>
+      <c r="A19" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>预计安装部署、卸载10月15日发布</t>
   </si>
@@ -88,65 +88,73 @@
     <t>卸载业务</t>
   </si>
   <si>
+    <t>页面优先显示</t>
+  </si>
+  <si>
+    <t>业务扩容</t>
+  </si>
+  <si>
+    <t>******</t>
+  </si>
+  <si>
+    <t>业务状态</t>
+  </si>
+  <si>
+    <t>启动业务</t>
+  </si>
+  <si>
+    <t>停止业务</t>
+  </si>
+  <si>
+    <t>许建辉、谭钊波、何嘉文、林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与会人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常处理(业务已经存在，版本冲突）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回值定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整为1个机器最耗时1s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>messageReply返回值的模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU占用 内存等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>开始编码，后台并发</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>页面优先显示</t>
-  </si>
-  <si>
-    <t>业务扩容</t>
-  </si>
-  <si>
-    <t>******</t>
-  </si>
-  <si>
-    <t>业务状态</t>
-  </si>
-  <si>
-    <t>启动业务</t>
-  </si>
-  <si>
-    <t>停止业务</t>
-  </si>
-  <si>
-    <t>许建辉、谭钊波、何嘉文、林友滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与会人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常处理(业务已经存在，版本冲突）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回值定义</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整为1个机器最耗时1s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待调试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>messageReply返回值的模式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测主机信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU占用 内存等</t>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -154,7 +162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +198,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -234,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -256,6 +271,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,10 +650,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27">
@@ -654,7 +675,9 @@
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
@@ -662,9 +685,11 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4">
@@ -672,7 +697,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -682,19 +707,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4">
@@ -728,41 +753,41 @@
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="4"/>
+      <c r="B14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="9"/>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4" ht="27">
       <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -775,40 +800,40 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -816,6 +841,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>预计安装部署、卸载10月15日发布</t>
   </si>
@@ -68,94 +68,111 @@
     <t>addhost</t>
   </si>
   <si>
+    <t>agent重启</t>
+  </si>
+  <si>
+    <t>卸载机器</t>
+  </si>
+  <si>
+    <t>卸载集群</t>
+  </si>
+  <si>
+    <t>卸载业务</t>
+  </si>
+  <si>
+    <t>页面优先显示</t>
+  </si>
+  <si>
+    <t>业务扩容</t>
+  </si>
+  <si>
+    <t>******</t>
+  </si>
+  <si>
+    <t>业务状态</t>
+  </si>
+  <si>
+    <t>启动业务</t>
+  </si>
+  <si>
+    <t>停止业务</t>
+  </si>
+  <si>
+    <t>许建辉、谭钊波、何嘉文、林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与会人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常处理(业务已经存在，版本冲突）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回值定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整为1个机器最耗时1s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待调试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>messageReply返回值的模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测主机信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU占用 内存等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始编码，后台并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>修改为后台并发</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>agent重启</t>
-  </si>
-  <si>
     <t>开始编码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>卸载机器</t>
-  </si>
-  <si>
-    <t>卸载集群</t>
-  </si>
-  <si>
-    <t>卸载业务</t>
-  </si>
-  <si>
-    <t>页面优先显示</t>
-  </si>
-  <si>
-    <t>业务扩容</t>
-  </si>
-  <si>
-    <t>******</t>
-  </si>
-  <si>
-    <t>业务状态</t>
-  </si>
-  <si>
-    <t>启动业务</t>
-  </si>
-  <si>
-    <t>停止业务</t>
-  </si>
-  <si>
-    <t>许建辉、谭钊波、何嘉文、林友滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与会人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常处理(业务已经存在，版本冲突）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回值定义</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整为1个机器最耗时1s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待调试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>messageReply返回值的模式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测主机信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU占用 内存等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始编码，后台并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林友滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何嘉文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不涉及</t>
+  </si>
+  <si>
+    <t>DOING</t>
   </si>
 </sst>
 </file>
@@ -222,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -245,11 +262,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -278,11 +319,157 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -640,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
@@ -648,27 +835,27 @@
     <col min="3" max="4" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="27">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="27">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="27">
+    <row r="4" spans="1:5" ht="27">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -676,170 +863,267 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
+        <v>29</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4">
+        <v>25</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="B14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" ht="27">
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:5" ht="27">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="12"/>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
+      <c r="E22" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:E22">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"不涉及"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"DOING"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:E22">
+      <formula1>"OK,DOING,不涉及"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
   <si>
     <t>预计安装部署、卸载10月15日发布</t>
   </si>
@@ -157,6 +157,10 @@
     <t>OK</t>
   </si>
   <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>谭钊波</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,7 +176,30 @@
     <t>不涉及</t>
   </si>
   <si>
+    <t>不涉及</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>DOING</t>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(完成获取网络流量的功能)</t>
+  </si>
+  <si>
+    <t>显示预计容量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户选中副本数和组数后，系统生成有效容量、总容量及冗余度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -362,6 +389,23 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="2" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -374,23 +418,6 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -827,12 +854,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.375" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1"/>
+    <col min="7" max="7" width="25.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -866,10 +894,10 @@
         <v>29</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -883,10 +911,10 @@
         <v>32</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -903,7 +931,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -914,13 +942,13 @@
         <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -931,13 +959,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -948,13 +976,13 @@
         <v>31</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -968,10 +996,10 @@
         <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -985,10 +1013,10 @@
         <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1002,10 +1030,10 @@
         <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1015,9 +1043,15 @@
       <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="12"/>
+      <c r="C15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="27">
       <c r="A16" s="3" t="s">
@@ -1026,11 +1060,17 @@
       <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="C16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -1038,36 +1078,45 @@
         <v>27</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="27">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="12"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>14</v>
@@ -1076,9 +1125,9 @@
       <c r="D20" s="6"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>14</v>
@@ -1087,9 +1136,9 @@
       <c r="D21" s="6"/>
       <c r="E21" s="12"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:7">
       <c r="A22" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>14</v>
@@ -1098,29 +1147,40 @@
       <c r="D22" s="6"/>
       <c r="E22" s="12"/>
     </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="12"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C7">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:E22">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"OK"</formula>
+  <conditionalFormatting sqref="C7:E23">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"DOING"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"不涉及"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"DOING"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:E22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:E23">
       <formula1>"OK,DOING,不涉及"</formula1>
     </dataValidation>
   </dataValidations>

--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -959,7 +959,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>39</v>

--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -357,7 +357,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="5">
     <dxf>
       <font>
         <b/>
@@ -403,98 +403,6 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1081,7 +989,7 @@
         <v>40</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>39</v>

--- a/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
+++ b/internal_doc/00.项目管理/01.会议纪要/2014.09.05 OM会议纪要.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>预计安装部署、卸载10月15日发布</t>
   </si>
@@ -199,6 +199,14 @@
   </si>
   <si>
     <t>DOING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不涉及</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不涉及</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -406,74 +414,6 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -485,7 +425,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -904,7 +844,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>39</v>
@@ -921,7 +861,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>39</v>
@@ -955,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>39</v>
